--- a/model_comb3/EvalOutputs/evaluation_metrics_TestDataset2.xlsx
+++ b/model_comb3/EvalOutputs/evaluation_metrics_TestDataset2.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2272</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2207</v>
+        <v>0.7601</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2223</v>
+        <v>0.7277</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1529</v>
+        <v>0.8988</v>
       </c>
     </row>
   </sheetData>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2824</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="3">
@@ -514,7 +514,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.352</v>
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Seg Threshold used</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -550,7 +560,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0098</v>
+        <v>0.1173</v>
       </c>
     </row>
     <row r="3">
@@ -560,7 +570,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0053</v>
+        <v>0.0751</v>
       </c>
     </row>
   </sheetData>
@@ -574,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B173"/>
+  <dimension ref="A1:B159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,1369 +609,1257 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.058621</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.013793</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07241400000000001</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.017241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.12069</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.027586</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.127586</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.034483</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.227586</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.048276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.227586</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.004444</v>
+        <v>0.055172</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.317241</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.004444</v>
+        <v>0.06551700000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.317241</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.008888999999999999</v>
+        <v>0.07241400000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.355172</v>
+        <v>0.004444</v>
       </c>
       <c r="B11" t="n">
-        <v>0.008888999999999999</v>
+        <v>0.075862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.362069</v>
+        <v>0.004444</v>
       </c>
       <c r="B12" t="n">
-        <v>0.008888999999999999</v>
+        <v>0.08620700000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.362069</v>
+        <v>0.004444</v>
       </c>
       <c r="B13" t="n">
-        <v>0.013333</v>
+        <v>0.09310300000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.410345</v>
+        <v>0.004444</v>
       </c>
       <c r="B14" t="n">
-        <v>0.013333</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.410345</v>
+        <v>0.004444</v>
       </c>
       <c r="B15" t="n">
-        <v>0.017778</v>
+        <v>0.106897</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.444828</v>
+        <v>0.004444</v>
       </c>
       <c r="B16" t="n">
-        <v>0.017778</v>
+        <v>0.162069</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.444828</v>
+        <v>0.004444</v>
       </c>
       <c r="B17" t="n">
-        <v>0.022222</v>
+        <v>0.168966</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.455172</v>
+        <v>0.004444</v>
       </c>
       <c r="B18" t="n">
-        <v>0.022222</v>
+        <v>0.17931</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.455172</v>
+        <v>0.004444</v>
       </c>
       <c r="B19" t="n">
-        <v>0.026667</v>
+        <v>0.186207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.472414</v>
+        <v>0.004444</v>
       </c>
       <c r="B20" t="n">
-        <v>0.026667</v>
+        <v>0.406897</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.472414</v>
+        <v>0.008888999999999999</v>
       </c>
       <c r="B21" t="n">
-        <v>0.031111</v>
+        <v>0.406897</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.482759</v>
+        <v>0.008888999999999999</v>
       </c>
       <c r="B22" t="n">
-        <v>0.031111</v>
+        <v>0.524138</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.482759</v>
+        <v>0.017778</v>
       </c>
       <c r="B23" t="n">
-        <v>0.035556</v>
+        <v>0.524138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.524138</v>
+        <v>0.017778</v>
       </c>
       <c r="B24" t="n">
-        <v>0.035556</v>
+        <v>0.548276</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.524138</v>
+        <v>0.017778</v>
       </c>
       <c r="B25" t="n">
-        <v>0.04</v>
+        <v>0.555172</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.531034</v>
+        <v>0.017778</v>
       </c>
       <c r="B26" t="n">
-        <v>0.04</v>
+        <v>0.572414</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.531034</v>
+        <v>0.022222</v>
       </c>
       <c r="B27" t="n">
-        <v>0.053333</v>
+        <v>0.572414</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.568966</v>
+        <v>0.022222</v>
       </c>
       <c r="B28" t="n">
-        <v>0.053333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.568966</v>
+        <v>0.026667</v>
       </c>
       <c r="B29" t="n">
-        <v>0.057778</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.589655</v>
+        <v>0.026667</v>
       </c>
       <c r="B30" t="n">
-        <v>0.057778</v>
+        <v>0.603448</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.589655</v>
+        <v>0.031111</v>
       </c>
       <c r="B31" t="n">
-        <v>0.062222</v>
+        <v>0.603448</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.596552</v>
+        <v>0.031111</v>
       </c>
       <c r="B32" t="n">
-        <v>0.062222</v>
+        <v>0.627586</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.596552</v>
+        <v>0.035556</v>
       </c>
       <c r="B33" t="n">
-        <v>0.066667</v>
+        <v>0.627586</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.606897</v>
+        <v>0.035556</v>
       </c>
       <c r="B34" t="n">
-        <v>0.066667</v>
+        <v>0.631034</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.606897</v>
+        <v>0.04</v>
       </c>
       <c r="B35" t="n">
-        <v>0.075556</v>
+        <v>0.631034</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.617241</v>
+        <v>0.04</v>
       </c>
       <c r="B36" t="n">
-        <v>0.075556</v>
+        <v>0.637931</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.617241</v>
+        <v>0.044444</v>
       </c>
       <c r="B37" t="n">
-        <v>0.08</v>
+        <v>0.637931</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.631034</v>
+        <v>0.044444</v>
       </c>
       <c r="B38" t="n">
-        <v>0.08</v>
+        <v>0.651724</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.631034</v>
+        <v>0.057778</v>
       </c>
       <c r="B39" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.651724</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.637931</v>
+        <v>0.057778</v>
       </c>
       <c r="B40" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.655172</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.637931</v>
+        <v>0.062222</v>
       </c>
       <c r="B41" t="n">
-        <v>0.088889</v>
+        <v>0.655172</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.648276</v>
+        <v>0.062222</v>
       </c>
       <c r="B42" t="n">
-        <v>0.088889</v>
+        <v>0.662069</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.648276</v>
+        <v>0.066667</v>
       </c>
       <c r="B43" t="n">
-        <v>0.097778</v>
+        <v>0.662069</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.655172</v>
+        <v>0.066667</v>
       </c>
       <c r="B44" t="n">
-        <v>0.097778</v>
+        <v>0.682759</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.662069</v>
+        <v>0.07111099999999999</v>
       </c>
       <c r="B45" t="n">
-        <v>0.097778</v>
+        <v>0.682759</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.662069</v>
+        <v>0.07111099999999999</v>
       </c>
       <c r="B46" t="n">
-        <v>0.102222</v>
+        <v>0.6965519999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.665517</v>
+        <v>0.075556</v>
       </c>
       <c r="B47" t="n">
-        <v>0.102222</v>
+        <v>0.6965519999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.665517</v>
+        <v>0.075556</v>
       </c>
       <c r="B48" t="n">
-        <v>0.115556</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.672414</v>
+        <v>0.08</v>
       </c>
       <c r="B49" t="n">
-        <v>0.115556</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.672414</v>
+        <v>0.08</v>
       </c>
       <c r="B50" t="n">
-        <v>0.137778</v>
+        <v>0.710345</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.682759</v>
+        <v>0.08444400000000001</v>
       </c>
       <c r="B51" t="n">
-        <v>0.137778</v>
+        <v>0.710345</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.682759</v>
+        <v>0.08444400000000001</v>
       </c>
       <c r="B52" t="n">
-        <v>0.146667</v>
+        <v>0.7241379999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.686207</v>
+        <v>0.088889</v>
       </c>
       <c r="B53" t="n">
-        <v>0.146667</v>
+        <v>0.7241379999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.693103</v>
+        <v>0.088889</v>
       </c>
       <c r="B54" t="n">
-        <v>0.146667</v>
+        <v>0.737931</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.710345</v>
+        <v>0.093333</v>
       </c>
       <c r="B55" t="n">
-        <v>0.146667</v>
+        <v>0.737931</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.710345</v>
+        <v>0.093333</v>
       </c>
       <c r="B56" t="n">
-        <v>0.155556</v>
+        <v>0.741379</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.717241</v>
+        <v>0.097778</v>
       </c>
       <c r="B57" t="n">
-        <v>0.155556</v>
+        <v>0.741379</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.717241</v>
+        <v>0.097778</v>
       </c>
       <c r="B58" t="n">
-        <v>0.16</v>
+        <v>0.758621</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.111111</v>
       </c>
       <c r="B59" t="n">
-        <v>0.16</v>
+        <v>0.758621</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.111111</v>
       </c>
       <c r="B60" t="n">
-        <v>0.164444</v>
+        <v>0.765517</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.727586</v>
+        <v>0.115556</v>
       </c>
       <c r="B61" t="n">
-        <v>0.164444</v>
+        <v>0.765517</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.727586</v>
+        <v>0.115556</v>
       </c>
       <c r="B62" t="n">
-        <v>0.168889</v>
+        <v>0.772414</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.731034</v>
+        <v>0.12</v>
       </c>
       <c r="B63" t="n">
-        <v>0.168889</v>
+        <v>0.772414</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.731034</v>
+        <v>0.12</v>
       </c>
       <c r="B64" t="n">
-        <v>0.173333</v>
+        <v>0.7793099999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.734483</v>
+        <v>0.124444</v>
       </c>
       <c r="B65" t="n">
-        <v>0.173333</v>
+        <v>0.7793099999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.734483</v>
+        <v>0.124444</v>
       </c>
       <c r="B66" t="n">
-        <v>0.186667</v>
+        <v>0.782759</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.737931</v>
+        <v>0.128889</v>
       </c>
       <c r="B67" t="n">
-        <v>0.186667</v>
+        <v>0.782759</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.737931</v>
+        <v>0.128889</v>
       </c>
       <c r="B68" t="n">
-        <v>0.195556</v>
+        <v>0.786207</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.7482760000000001</v>
+        <v>0.133333</v>
       </c>
       <c r="B69" t="n">
-        <v>0.195556</v>
+        <v>0.786207</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.7482760000000001</v>
+        <v>0.133333</v>
       </c>
       <c r="B70" t="n">
-        <v>0.2</v>
+        <v>0.789655</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.755172</v>
+        <v>0.142222</v>
       </c>
       <c r="B71" t="n">
-        <v>0.2</v>
+        <v>0.789655</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.755172</v>
+        <v>0.142222</v>
       </c>
       <c r="B72" t="n">
-        <v>0.217778</v>
+        <v>0.793103</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.758621</v>
+        <v>0.146667</v>
       </c>
       <c r="B73" t="n">
-        <v>0.217778</v>
+        <v>0.793103</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.758621</v>
+        <v>0.146667</v>
       </c>
       <c r="B74" t="n">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.765517</v>
+        <v>0.155556</v>
       </c>
       <c r="B75" t="n">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.765517</v>
+        <v>0.155556</v>
       </c>
       <c r="B76" t="n">
-        <v>0.244444</v>
+        <v>0.806897</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.7758620000000001</v>
+        <v>0.16</v>
       </c>
       <c r="B77" t="n">
-        <v>0.244444</v>
+        <v>0.806897</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.7758620000000001</v>
+        <v>0.16</v>
       </c>
       <c r="B78" t="n">
-        <v>0.257778</v>
+        <v>0.834483</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.7793099999999999</v>
+        <v>0.173333</v>
       </c>
       <c r="B79" t="n">
-        <v>0.257778</v>
+        <v>0.834483</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.7793099999999999</v>
+        <v>0.173333</v>
       </c>
       <c r="B80" t="n">
-        <v>0.266667</v>
+        <v>0.851724</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.786207</v>
+        <v>0.177778</v>
       </c>
       <c r="B81" t="n">
-        <v>0.266667</v>
+        <v>0.851724</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.786207</v>
+        <v>0.177778</v>
       </c>
       <c r="B82" t="n">
-        <v>0.271111</v>
+        <v>0.855172</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.789655</v>
+        <v>0.191111</v>
       </c>
       <c r="B83" t="n">
-        <v>0.271111</v>
+        <v>0.855172</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.789655</v>
+        <v>0.191111</v>
       </c>
       <c r="B84" t="n">
-        <v>0.28</v>
+        <v>0.858621</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.793103</v>
+        <v>0.204444</v>
       </c>
       <c r="B85" t="n">
-        <v>0.28</v>
+        <v>0.858621</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.793103</v>
+        <v>0.204444</v>
       </c>
       <c r="B86" t="n">
-        <v>0.293333</v>
+        <v>0.862069</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.806897</v>
+        <v>0.222222</v>
       </c>
       <c r="B87" t="n">
-        <v>0.293333</v>
+        <v>0.862069</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.806897</v>
+        <v>0.222222</v>
       </c>
       <c r="B88" t="n">
-        <v>0.302222</v>
+        <v>0.872414</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.813793</v>
+        <v>0.231111</v>
       </c>
       <c r="B89" t="n">
-        <v>0.302222</v>
+        <v>0.872414</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.817241</v>
+        <v>0.231111</v>
       </c>
       <c r="B90" t="n">
-        <v>0.302222</v>
+        <v>0.875862</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.817241</v>
+        <v>0.235556</v>
       </c>
       <c r="B91" t="n">
-        <v>0.306667</v>
+        <v>0.875862</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.824138</v>
+        <v>0.235556</v>
       </c>
       <c r="B92" t="n">
-        <v>0.306667</v>
+        <v>0.87931</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.824138</v>
+        <v>0.248889</v>
       </c>
       <c r="B93" t="n">
-        <v>0.32</v>
+        <v>0.87931</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.827586</v>
+        <v>0.248889</v>
       </c>
       <c r="B94" t="n">
-        <v>0.32</v>
+        <v>0.882759</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.827586</v>
+        <v>0.253333</v>
       </c>
       <c r="B95" t="n">
-        <v>0.328889</v>
+        <v>0.882759</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.837931</v>
+        <v>0.253333</v>
       </c>
       <c r="B96" t="n">
-        <v>0.328889</v>
+        <v>0.886207</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.837931</v>
+        <v>0.311111</v>
       </c>
       <c r="B97" t="n">
-        <v>0.342222</v>
+        <v>0.886207</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.841379</v>
+        <v>0.311111</v>
       </c>
       <c r="B98" t="n">
-        <v>0.342222</v>
+        <v>0.889655</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.841379</v>
+        <v>0.32</v>
       </c>
       <c r="B99" t="n">
-        <v>0.346667</v>
+        <v>0.889655</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.844828</v>
+        <v>0.32</v>
       </c>
       <c r="B100" t="n">
-        <v>0.346667</v>
+        <v>0.893103</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.844828</v>
+        <v>0.328889</v>
       </c>
       <c r="B101" t="n">
-        <v>0.351111</v>
+        <v>0.893103</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0.855172</v>
+        <v>0.328889</v>
       </c>
       <c r="B102" t="n">
-        <v>0.351111</v>
+        <v>0.896552</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.855172</v>
+        <v>0.364444</v>
       </c>
       <c r="B103" t="n">
-        <v>0.391111</v>
+        <v>0.896552</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.858621</v>
+        <v>0.364444</v>
       </c>
       <c r="B104" t="n">
-        <v>0.391111</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.858621</v>
+        <v>0.391111</v>
       </c>
       <c r="B105" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.862069</v>
+        <v>0.391111</v>
       </c>
       <c r="B106" t="n">
-        <v>0.4</v>
+        <v>0.906897</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.862069</v>
+        <v>0.413333</v>
       </c>
       <c r="B107" t="n">
-        <v>0.413333</v>
+        <v>0.906897</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.865517</v>
+        <v>0.413333</v>
       </c>
       <c r="B108" t="n">
-        <v>0.413333</v>
+        <v>0.910345</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0.865517</v>
+        <v>0.417778</v>
       </c>
       <c r="B109" t="n">
-        <v>0.422222</v>
+        <v>0.910345</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0.868966</v>
+        <v>0.417778</v>
       </c>
       <c r="B110" t="n">
-        <v>0.422222</v>
+        <v>0.913793</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.868966</v>
+        <v>0.426667</v>
       </c>
       <c r="B111" t="n">
-        <v>0.44</v>
+        <v>0.913793</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>0.875862</v>
+        <v>0.426667</v>
       </c>
       <c r="B112" t="n">
-        <v>0.44</v>
+        <v>0.917241</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0.875862</v>
+        <v>0.431111</v>
       </c>
       <c r="B113" t="n">
-        <v>0.448889</v>
+        <v>0.917241</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0.87931</v>
+        <v>0.431111</v>
       </c>
       <c r="B114" t="n">
-        <v>0.448889</v>
+        <v>0.92069</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0.87931</v>
+        <v>0.448889</v>
       </c>
       <c r="B115" t="n">
-        <v>0.475556</v>
+        <v>0.92069</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.882759</v>
+        <v>0.448889</v>
       </c>
       <c r="B116" t="n">
-        <v>0.475556</v>
+        <v>0.924138</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0.882759</v>
+        <v>0.462222</v>
       </c>
       <c r="B117" t="n">
-        <v>0.493333</v>
+        <v>0.924138</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0.886207</v>
+        <v>0.462222</v>
       </c>
       <c r="B118" t="n">
-        <v>0.493333</v>
+        <v>0.927586</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.886207</v>
+        <v>0.493333</v>
       </c>
       <c r="B119" t="n">
-        <v>0.506667</v>
+        <v>0.927586</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0.896552</v>
+        <v>0.493333</v>
       </c>
       <c r="B120" t="n">
-        <v>0.506667</v>
+        <v>0.931034</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0.896552</v>
+        <v>0.5022219999999999</v>
       </c>
       <c r="B121" t="n">
-        <v>0.515556</v>
+        <v>0.931034</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0.9</v>
+        <v>0.5022219999999999</v>
       </c>
       <c r="B122" t="n">
-        <v>0.515556</v>
+        <v>0.934483</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>0.9</v>
+        <v>0.506667</v>
       </c>
       <c r="B123" t="n">
-        <v>0.524444</v>
+        <v>0.934483</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0.903448</v>
+        <v>0.506667</v>
       </c>
       <c r="B124" t="n">
-        <v>0.524444</v>
+        <v>0.937931</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>0.903448</v>
+        <v>0.524444</v>
       </c>
       <c r="B125" t="n">
-        <v>0.5288890000000001</v>
+        <v>0.937931</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>0.910345</v>
+        <v>0.524444</v>
       </c>
       <c r="B126" t="n">
-        <v>0.5288890000000001</v>
+        <v>0.941379</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0.910345</v>
+        <v>0.5288890000000001</v>
       </c>
       <c r="B127" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.941379</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0.913793</v>
+        <v>0.5288890000000001</v>
       </c>
       <c r="B128" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.944828</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0.913793</v>
+        <v>0.573333</v>
       </c>
       <c r="B129" t="n">
-        <v>0.5644439999999999</v>
+        <v>0.944828</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0.917241</v>
+        <v>0.573333</v>
       </c>
       <c r="B130" t="n">
-        <v>0.5644439999999999</v>
+        <v>0.948276</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0.917241</v>
+        <v>0.577778</v>
       </c>
       <c r="B131" t="n">
-        <v>0.577778</v>
+        <v>0.948276</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0.92069</v>
+        <v>0.577778</v>
       </c>
       <c r="B132" t="n">
-        <v>0.577778</v>
+        <v>0.951724</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>0.92069</v>
+        <v>0.595556</v>
       </c>
       <c r="B133" t="n">
-        <v>0.582222</v>
+        <v>0.951724</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0.924138</v>
+        <v>0.595556</v>
       </c>
       <c r="B134" t="n">
-        <v>0.582222</v>
+        <v>0.955172</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0.924138</v>
+        <v>0.6222220000000001</v>
       </c>
       <c r="B135" t="n">
-        <v>0.5911110000000001</v>
+        <v>0.955172</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0.927586</v>
+        <v>0.6222220000000001</v>
       </c>
       <c r="B136" t="n">
-        <v>0.5911110000000001</v>
+        <v>0.9586209999999999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0.927586</v>
+        <v>0.626667</v>
       </c>
       <c r="B137" t="n">
-        <v>0.6</v>
+        <v>0.9586209999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0.931034</v>
+        <v>0.626667</v>
       </c>
       <c r="B138" t="n">
-        <v>0.6</v>
+        <v>0.965517</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0.931034</v>
+        <v>0.657778</v>
       </c>
       <c r="B139" t="n">
-        <v>0.626667</v>
+        <v>0.965517</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0.934483</v>
+        <v>0.657778</v>
       </c>
       <c r="B140" t="n">
-        <v>0.626667</v>
+        <v>0.968966</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0.934483</v>
+        <v>0.728889</v>
       </c>
       <c r="B141" t="n">
-        <v>0.675556</v>
+        <v>0.968966</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0.937931</v>
+        <v>0.728889</v>
       </c>
       <c r="B142" t="n">
-        <v>0.675556</v>
+        <v>0.972414</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0.937931</v>
+        <v>0.751111</v>
       </c>
       <c r="B143" t="n">
-        <v>0.68</v>
+        <v>0.972414</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0.941379</v>
+        <v>0.751111</v>
       </c>
       <c r="B144" t="n">
-        <v>0.68</v>
+        <v>0.975862</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0.941379</v>
+        <v>0.76</v>
       </c>
       <c r="B145" t="n">
-        <v>0.693333</v>
+        <v>0.975862</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0.944828</v>
+        <v>0.76</v>
       </c>
       <c r="B146" t="n">
-        <v>0.693333</v>
+        <v>0.97931</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0.944828</v>
+        <v>0.822222</v>
       </c>
       <c r="B147" t="n">
-        <v>0.697778</v>
+        <v>0.97931</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>0.951724</v>
+        <v>0.822222</v>
       </c>
       <c r="B148" t="n">
-        <v>0.697778</v>
+        <v>0.982759</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0.951724</v>
+        <v>0.831111</v>
       </c>
       <c r="B149" t="n">
-        <v>0.773333</v>
+        <v>0.982759</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>0.955172</v>
+        <v>0.831111</v>
       </c>
       <c r="B150" t="n">
-        <v>0.773333</v>
+        <v>0.9862069999999999</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>0.955172</v>
+        <v>0.848889</v>
       </c>
       <c r="B151" t="n">
-        <v>0.777778</v>
+        <v>0.9862069999999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.9586209999999999</v>
+        <v>0.848889</v>
       </c>
       <c r="B152" t="n">
-        <v>0.777778</v>
+        <v>0.989655</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0.9586209999999999</v>
+        <v>0.866667</v>
       </c>
       <c r="B153" t="n">
-        <v>0.795556</v>
+        <v>0.989655</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0.962069</v>
+        <v>0.866667</v>
       </c>
       <c r="B154" t="n">
-        <v>0.795556</v>
+        <v>0.993103</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0.962069</v>
+        <v>0.915556</v>
       </c>
       <c r="B155" t="n">
-        <v>0.8</v>
+        <v>0.993103</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0.965517</v>
+        <v>0.915556</v>
       </c>
       <c r="B156" t="n">
-        <v>0.8</v>
+        <v>0.996552</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>0.965517</v>
+        <v>0.942222</v>
       </c>
       <c r="B157" t="n">
-        <v>0.853333</v>
+        <v>0.996552</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>0.968966</v>
+        <v>0.942222</v>
       </c>
       <c r="B158" t="n">
-        <v>0.853333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>0.968966</v>
+        <v>1</v>
       </c>
       <c r="B159" t="n">
-        <v>0.866667</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>0.972414</v>
-      </c>
-      <c r="B160" t="n">
-        <v>0.866667</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>0.972414</v>
-      </c>
-      <c r="B161" t="n">
-        <v>0.888889</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>0.975862</v>
-      </c>
-      <c r="B162" t="n">
-        <v>0.888889</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>0.975862</v>
-      </c>
-      <c r="B163" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>0.97931</v>
-      </c>
-      <c r="B164" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>0.97931</v>
-      </c>
-      <c r="B165" t="n">
-        <v>0.942222</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>0.982759</v>
-      </c>
-      <c r="B166" t="n">
-        <v>0.942222</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>0.982759</v>
-      </c>
-      <c r="B167" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>0.9862069999999999</v>
-      </c>
-      <c r="B168" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>0.9862069999999999</v>
-      </c>
-      <c r="B169" t="n">
-        <v>0.973333</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>0.989655</v>
-      </c>
-      <c r="B170" t="n">
-        <v>0.973333</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>0.989655</v>
-      </c>
-      <c r="B171" t="n">
-        <v>0.977778</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>1</v>
-      </c>
-      <c r="B172" t="n">
-        <v>0.977778</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>1</v>
-      </c>
-      <c r="B173" t="n">
         <v>1</v>
       </c>
     </row>

--- a/model_comb3/EvalOutputs/evaluation_metrics_TestDataset2.xlsx
+++ b/model_comb3/EvalOutputs/evaluation_metrics_TestDataset2.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.732</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7601</v>
+        <v>0.6714</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7277</v>
+        <v>0.6191</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8988</v>
+        <v>0.824</v>
       </c>
     </row>
   </sheetData>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.927</v>
+        <v>0.8666</v>
       </c>
     </row>
     <row r="3">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001</v>
+        <v>0.3725</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1173</v>
+        <v>0.5339</v>
       </c>
     </row>
     <row r="3">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0751</v>
+        <v>0.4356</v>
       </c>
     </row>
   </sheetData>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B159"/>
+  <dimension ref="A1:B194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.013793</v>
+        <v>0.003448</v>
       </c>
     </row>
     <row r="4">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.017241</v>
+        <v>0.010345</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.027586</v>
+        <v>0.017241</v>
       </c>
     </row>
     <row r="6">
@@ -636,663 +636,663 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.034483</v>
+        <v>0.055172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>0.004444</v>
       </c>
       <c r="B7" t="n">
-        <v>0.048276</v>
+        <v>0.055172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>0.004444</v>
       </c>
       <c r="B8" t="n">
-        <v>0.055172</v>
+        <v>0.148276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>0.008888999999999999</v>
       </c>
       <c r="B9" t="n">
-        <v>0.06551700000000001</v>
+        <v>0.148276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>0.008888999999999999</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07241400000000001</v>
+        <v>0.186207</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.004444</v>
+        <v>0.008888999999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>0.075862</v>
+        <v>0.193103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.004444</v>
+        <v>0.008888999999999999</v>
       </c>
       <c r="B12" t="n">
-        <v>0.08620700000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.004444</v>
+        <v>0.013333</v>
       </c>
       <c r="B13" t="n">
-        <v>0.09310300000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.004444</v>
+        <v>0.013333</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1</v>
+        <v>0.227586</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.004444</v>
+        <v>0.013333</v>
       </c>
       <c r="B15" t="n">
-        <v>0.106897</v>
+        <v>0.234483</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.004444</v>
+        <v>0.013333</v>
       </c>
       <c r="B16" t="n">
-        <v>0.162069</v>
+        <v>0.289655</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.004444</v>
+        <v>0.017778</v>
       </c>
       <c r="B17" t="n">
-        <v>0.168966</v>
+        <v>0.289655</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.004444</v>
+        <v>0.017778</v>
       </c>
       <c r="B18" t="n">
-        <v>0.17931</v>
+        <v>0.306897</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.004444</v>
+        <v>0.022222</v>
       </c>
       <c r="B19" t="n">
-        <v>0.186207</v>
+        <v>0.306897</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.004444</v>
+        <v>0.022222</v>
       </c>
       <c r="B20" t="n">
-        <v>0.406897</v>
+        <v>0.348276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.008888999999999999</v>
+        <v>0.026667</v>
       </c>
       <c r="B21" t="n">
-        <v>0.406897</v>
+        <v>0.348276</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.008888999999999999</v>
+        <v>0.026667</v>
       </c>
       <c r="B22" t="n">
-        <v>0.524138</v>
+        <v>0.362069</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.017778</v>
+        <v>0.035556</v>
       </c>
       <c r="B23" t="n">
-        <v>0.524138</v>
+        <v>0.362069</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.017778</v>
+        <v>0.035556</v>
       </c>
       <c r="B24" t="n">
-        <v>0.548276</v>
+        <v>0.375862</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.017778</v>
+        <v>0.04</v>
       </c>
       <c r="B25" t="n">
-        <v>0.555172</v>
+        <v>0.375862</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.017778</v>
+        <v>0.04</v>
       </c>
       <c r="B26" t="n">
-        <v>0.572414</v>
+        <v>0.403448</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.022222</v>
+        <v>0.044444</v>
       </c>
       <c r="B27" t="n">
-        <v>0.572414</v>
+        <v>0.403448</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.022222</v>
+        <v>0.044444</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6</v>
+        <v>0.417241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.026667</v>
+        <v>0.048889</v>
       </c>
       <c r="B29" t="n">
-        <v>0.6</v>
+        <v>0.417241</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.026667</v>
+        <v>0.048889</v>
       </c>
       <c r="B30" t="n">
-        <v>0.603448</v>
+        <v>0.441379</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.031111</v>
+        <v>0.053333</v>
       </c>
       <c r="B31" t="n">
-        <v>0.603448</v>
+        <v>0.441379</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.031111</v>
+        <v>0.053333</v>
       </c>
       <c r="B32" t="n">
-        <v>0.627586</v>
+        <v>0.448276</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.035556</v>
+        <v>0.062222</v>
       </c>
       <c r="B33" t="n">
-        <v>0.627586</v>
+        <v>0.448276</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.035556</v>
+        <v>0.062222</v>
       </c>
       <c r="B34" t="n">
-        <v>0.631034</v>
+        <v>0.451724</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.04</v>
+        <v>0.066667</v>
       </c>
       <c r="B35" t="n">
-        <v>0.631034</v>
+        <v>0.451724</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.04</v>
+        <v>0.066667</v>
       </c>
       <c r="B36" t="n">
-        <v>0.637931</v>
+        <v>0.458621</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.044444</v>
+        <v>0.07111099999999999</v>
       </c>
       <c r="B37" t="n">
-        <v>0.637931</v>
+        <v>0.458621</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.044444</v>
+        <v>0.07111099999999999</v>
       </c>
       <c r="B38" t="n">
-        <v>0.651724</v>
+        <v>0.462069</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.057778</v>
+        <v>0.075556</v>
       </c>
       <c r="B39" t="n">
-        <v>0.651724</v>
+        <v>0.462069</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.057778</v>
+        <v>0.075556</v>
       </c>
       <c r="B40" t="n">
-        <v>0.655172</v>
+        <v>0.468966</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.062222</v>
+        <v>0.08</v>
       </c>
       <c r="B41" t="n">
-        <v>0.655172</v>
+        <v>0.468966</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.062222</v>
+        <v>0.08</v>
       </c>
       <c r="B42" t="n">
-        <v>0.662069</v>
+        <v>0.482759</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.066667</v>
+        <v>0.08444400000000001</v>
       </c>
       <c r="B43" t="n">
-        <v>0.662069</v>
+        <v>0.482759</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.066667</v>
+        <v>0.08444400000000001</v>
       </c>
       <c r="B44" t="n">
-        <v>0.682759</v>
+        <v>0.503448</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.07111099999999999</v>
+        <v>0.088889</v>
       </c>
       <c r="B45" t="n">
-        <v>0.682759</v>
+        <v>0.503448</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.07111099999999999</v>
+        <v>0.088889</v>
       </c>
       <c r="B46" t="n">
-        <v>0.6965519999999999</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.075556</v>
+        <v>0.097778</v>
       </c>
       <c r="B47" t="n">
-        <v>0.6965519999999999</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.075556</v>
+        <v>0.097778</v>
       </c>
       <c r="B48" t="n">
-        <v>0.7</v>
+        <v>0.603448</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.08</v>
+        <v>0.102222</v>
       </c>
       <c r="B49" t="n">
-        <v>0.7</v>
+        <v>0.603448</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.08</v>
+        <v>0.102222</v>
       </c>
       <c r="B50" t="n">
-        <v>0.710345</v>
+        <v>0.606897</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.106667</v>
       </c>
       <c r="B51" t="n">
-        <v>0.710345</v>
+        <v>0.606897</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.106667</v>
       </c>
       <c r="B52" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.617241</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.088889</v>
+        <v>0.111111</v>
       </c>
       <c r="B53" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.617241</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.088889</v>
+        <v>0.111111</v>
       </c>
       <c r="B54" t="n">
-        <v>0.737931</v>
+        <v>0.62069</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.093333</v>
+        <v>0.115556</v>
       </c>
       <c r="B55" t="n">
-        <v>0.737931</v>
+        <v>0.62069</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.093333</v>
+        <v>0.115556</v>
       </c>
       <c r="B56" t="n">
-        <v>0.741379</v>
+        <v>0.648276</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.097778</v>
+        <v>0.12</v>
       </c>
       <c r="B57" t="n">
-        <v>0.741379</v>
+        <v>0.648276</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.097778</v>
+        <v>0.12</v>
       </c>
       <c r="B58" t="n">
-        <v>0.758621</v>
+        <v>0.651724</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.111111</v>
+        <v>0.128889</v>
       </c>
       <c r="B59" t="n">
-        <v>0.758621</v>
+        <v>0.651724</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.111111</v>
+        <v>0.128889</v>
       </c>
       <c r="B60" t="n">
-        <v>0.765517</v>
+        <v>0.655172</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.115556</v>
+        <v>0.146667</v>
       </c>
       <c r="B61" t="n">
-        <v>0.765517</v>
+        <v>0.655172</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.115556</v>
+        <v>0.146667</v>
       </c>
       <c r="B62" t="n">
-        <v>0.772414</v>
+        <v>0.662069</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.12</v>
+        <v>0.146667</v>
       </c>
       <c r="B63" t="n">
-        <v>0.772414</v>
+        <v>0.6689659999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.12</v>
+        <v>0.151111</v>
       </c>
       <c r="B64" t="n">
-        <v>0.7793099999999999</v>
+        <v>0.6689659999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.124444</v>
+        <v>0.151111</v>
       </c>
       <c r="B65" t="n">
-        <v>0.7793099999999999</v>
+        <v>0.67931</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.124444</v>
+        <v>0.155556</v>
       </c>
       <c r="B66" t="n">
-        <v>0.782759</v>
+        <v>0.67931</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.128889</v>
+        <v>0.155556</v>
       </c>
       <c r="B67" t="n">
-        <v>0.782759</v>
+        <v>0.689655</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.128889</v>
+        <v>0.16</v>
       </c>
       <c r="B68" t="n">
-        <v>0.786207</v>
+        <v>0.689655</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.133333</v>
+        <v>0.16</v>
       </c>
       <c r="B69" t="n">
-        <v>0.786207</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.133333</v>
+        <v>0.164444</v>
       </c>
       <c r="B70" t="n">
-        <v>0.789655</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.142222</v>
+        <v>0.164444</v>
       </c>
       <c r="B71" t="n">
-        <v>0.789655</v>
+        <v>0.7241379999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.142222</v>
+        <v>0.168889</v>
       </c>
       <c r="B72" t="n">
-        <v>0.793103</v>
+        <v>0.7241379999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.146667</v>
+        <v>0.168889</v>
       </c>
       <c r="B73" t="n">
-        <v>0.793103</v>
+        <v>0.727586</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.146667</v>
+        <v>0.177778</v>
       </c>
       <c r="B74" t="n">
-        <v>0.8</v>
+        <v>0.727586</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.155556</v>
+        <v>0.177778</v>
       </c>
       <c r="B75" t="n">
-        <v>0.8</v>
+        <v>0.731034</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.155556</v>
+        <v>0.195556</v>
       </c>
       <c r="B76" t="n">
-        <v>0.806897</v>
+        <v>0.731034</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.16</v>
+        <v>0.195556</v>
       </c>
       <c r="B77" t="n">
-        <v>0.806897</v>
+        <v>0.734483</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="B78" t="n">
-        <v>0.834483</v>
+        <v>0.734483</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.173333</v>
+        <v>0.2</v>
       </c>
       <c r="B79" t="n">
-        <v>0.834483</v>
+        <v>0.741379</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.173333</v>
+        <v>0.204444</v>
       </c>
       <c r="B80" t="n">
-        <v>0.851724</v>
+        <v>0.741379</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.177778</v>
+        <v>0.204444</v>
       </c>
       <c r="B81" t="n">
-        <v>0.851724</v>
+        <v>0.744828</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.177778</v>
+        <v>0.213333</v>
       </c>
       <c r="B82" t="n">
-        <v>0.855172</v>
+        <v>0.744828</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.191111</v>
+        <v>0.213333</v>
       </c>
       <c r="B83" t="n">
-        <v>0.855172</v>
+        <v>0.7482760000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.191111</v>
+        <v>0.217778</v>
       </c>
       <c r="B84" t="n">
-        <v>0.858621</v>
+        <v>0.7482760000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.204444</v>
+        <v>0.217778</v>
       </c>
       <c r="B85" t="n">
-        <v>0.858621</v>
+        <v>0.7517239999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.204444</v>
+        <v>0.226667</v>
       </c>
       <c r="B86" t="n">
-        <v>0.862069</v>
+        <v>0.7517239999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.222222</v>
+        <v>0.226667</v>
       </c>
       <c r="B87" t="n">
-        <v>0.862069</v>
+        <v>0.755172</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.222222</v>
+        <v>0.231111</v>
       </c>
       <c r="B88" t="n">
-        <v>0.872414</v>
+        <v>0.755172</v>
       </c>
     </row>
     <row r="89">
@@ -1300,15 +1300,15 @@
         <v>0.231111</v>
       </c>
       <c r="B89" t="n">
-        <v>0.872414</v>
+        <v>0.758621</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.231111</v>
+        <v>0.235556</v>
       </c>
       <c r="B90" t="n">
-        <v>0.875862</v>
+        <v>0.758621</v>
       </c>
     </row>
     <row r="91">
@@ -1316,550 +1316,830 @@
         <v>0.235556</v>
       </c>
       <c r="B91" t="n">
-        <v>0.875862</v>
+        <v>0.762069</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.235556</v>
+        <v>0.24</v>
       </c>
       <c r="B92" t="n">
-        <v>0.87931</v>
+        <v>0.762069</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.248889</v>
+        <v>0.24</v>
       </c>
       <c r="B93" t="n">
-        <v>0.87931</v>
+        <v>0.765517</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.248889</v>
+        <v>0.244444</v>
       </c>
       <c r="B94" t="n">
-        <v>0.882759</v>
+        <v>0.765517</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.253333</v>
+        <v>0.244444</v>
       </c>
       <c r="B95" t="n">
-        <v>0.882759</v>
+        <v>0.772414</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.253333</v>
+        <v>0.248889</v>
       </c>
       <c r="B96" t="n">
-        <v>0.886207</v>
+        <v>0.772414</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.311111</v>
+        <v>0.248889</v>
       </c>
       <c r="B97" t="n">
-        <v>0.886207</v>
+        <v>0.782759</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.311111</v>
+        <v>0.253333</v>
       </c>
       <c r="B98" t="n">
-        <v>0.889655</v>
+        <v>0.782759</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.32</v>
+        <v>0.253333</v>
       </c>
       <c r="B99" t="n">
-        <v>0.889655</v>
+        <v>0.786207</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.32</v>
+        <v>0.262222</v>
       </c>
       <c r="B100" t="n">
-        <v>0.893103</v>
+        <v>0.786207</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.328889</v>
+        <v>0.262222</v>
       </c>
       <c r="B101" t="n">
-        <v>0.893103</v>
+        <v>0.789655</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0.328889</v>
+        <v>0.271111</v>
       </c>
       <c r="B102" t="n">
-        <v>0.896552</v>
+        <v>0.789655</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.364444</v>
+        <v>0.271111</v>
       </c>
       <c r="B103" t="n">
-        <v>0.896552</v>
+        <v>0.796552</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.364444</v>
+        <v>0.275556</v>
       </c>
       <c r="B104" t="n">
-        <v>0.9</v>
+        <v>0.796552</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.391111</v>
+        <v>0.275556</v>
       </c>
       <c r="B105" t="n">
-        <v>0.9</v>
+        <v>0.8034480000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.391111</v>
+        <v>0.28</v>
       </c>
       <c r="B106" t="n">
-        <v>0.906897</v>
+        <v>0.8034480000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.413333</v>
+        <v>0.28</v>
       </c>
       <c r="B107" t="n">
-        <v>0.906897</v>
+        <v>0.806897</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.413333</v>
+        <v>0.288889</v>
       </c>
       <c r="B108" t="n">
-        <v>0.910345</v>
+        <v>0.806897</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0.417778</v>
+        <v>0.288889</v>
       </c>
       <c r="B109" t="n">
-        <v>0.910345</v>
+        <v>0.810345</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0.417778</v>
+        <v>0.302222</v>
       </c>
       <c r="B110" t="n">
-        <v>0.913793</v>
+        <v>0.810345</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.426667</v>
+        <v>0.302222</v>
       </c>
       <c r="B111" t="n">
-        <v>0.913793</v>
+        <v>0.813793</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>0.426667</v>
+        <v>0.306667</v>
       </c>
       <c r="B112" t="n">
-        <v>0.917241</v>
+        <v>0.813793</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0.431111</v>
+        <v>0.306667</v>
       </c>
       <c r="B113" t="n">
-        <v>0.917241</v>
+        <v>0.82069</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0.431111</v>
+        <v>0.324444</v>
       </c>
       <c r="B114" t="n">
-        <v>0.92069</v>
+        <v>0.82069</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0.448889</v>
+        <v>0.324444</v>
       </c>
       <c r="B115" t="n">
-        <v>0.92069</v>
+        <v>0.824138</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.448889</v>
+        <v>0.337778</v>
       </c>
       <c r="B116" t="n">
-        <v>0.924138</v>
+        <v>0.824138</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0.462222</v>
+        <v>0.337778</v>
       </c>
       <c r="B117" t="n">
-        <v>0.924138</v>
+        <v>0.827586</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0.462222</v>
+        <v>0.342222</v>
       </c>
       <c r="B118" t="n">
-        <v>0.927586</v>
+        <v>0.827586</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.493333</v>
+        <v>0.342222</v>
       </c>
       <c r="B119" t="n">
-        <v>0.927586</v>
+        <v>0.8310340000000001</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0.493333</v>
+        <v>0.351111</v>
       </c>
       <c r="B120" t="n">
-        <v>0.931034</v>
+        <v>0.8310340000000001</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0.5022219999999999</v>
+        <v>0.351111</v>
       </c>
       <c r="B121" t="n">
-        <v>0.931034</v>
+        <v>0.834483</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0.5022219999999999</v>
+        <v>0.355556</v>
       </c>
       <c r="B122" t="n">
-        <v>0.934483</v>
+        <v>0.834483</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>0.506667</v>
+        <v>0.355556</v>
       </c>
       <c r="B123" t="n">
-        <v>0.934483</v>
+        <v>0.837931</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0.506667</v>
+        <v>0.377778</v>
       </c>
       <c r="B124" t="n">
-        <v>0.937931</v>
+        <v>0.837931</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>0.524444</v>
+        <v>0.377778</v>
       </c>
       <c r="B125" t="n">
-        <v>0.937931</v>
+        <v>0.844828</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>0.524444</v>
+        <v>0.4</v>
       </c>
       <c r="B126" t="n">
-        <v>0.941379</v>
+        <v>0.844828</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0.5288890000000001</v>
+        <v>0.4</v>
       </c>
       <c r="B127" t="n">
-        <v>0.941379</v>
+        <v>0.848276</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0.5288890000000001</v>
+        <v>0.408889</v>
       </c>
       <c r="B128" t="n">
-        <v>0.944828</v>
+        <v>0.848276</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0.573333</v>
+        <v>0.408889</v>
       </c>
       <c r="B129" t="n">
-        <v>0.944828</v>
+        <v>0.851724</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0.573333</v>
+        <v>0.413333</v>
       </c>
       <c r="B130" t="n">
-        <v>0.948276</v>
+        <v>0.851724</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0.577778</v>
+        <v>0.413333</v>
       </c>
       <c r="B131" t="n">
-        <v>0.948276</v>
+        <v>0.855172</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0.577778</v>
+        <v>0.426667</v>
       </c>
       <c r="B132" t="n">
-        <v>0.951724</v>
+        <v>0.855172</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>0.595556</v>
+        <v>0.426667</v>
       </c>
       <c r="B133" t="n">
-        <v>0.951724</v>
+        <v>0.858621</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0.595556</v>
+        <v>0.44</v>
       </c>
       <c r="B134" t="n">
-        <v>0.955172</v>
+        <v>0.858621</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0.6222220000000001</v>
+        <v>0.44</v>
       </c>
       <c r="B135" t="n">
-        <v>0.955172</v>
+        <v>0.862069</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0.6222220000000001</v>
+        <v>0.444444</v>
       </c>
       <c r="B136" t="n">
-        <v>0.9586209999999999</v>
+        <v>0.862069</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0.626667</v>
+        <v>0.444444</v>
       </c>
       <c r="B137" t="n">
-        <v>0.9586209999999999</v>
+        <v>0.865517</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0.626667</v>
+        <v>0.448889</v>
       </c>
       <c r="B138" t="n">
-        <v>0.965517</v>
+        <v>0.865517</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0.657778</v>
+        <v>0.448889</v>
       </c>
       <c r="B139" t="n">
-        <v>0.965517</v>
+        <v>0.868966</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0.657778</v>
+        <v>0.453333</v>
       </c>
       <c r="B140" t="n">
-        <v>0.968966</v>
+        <v>0.868966</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0.728889</v>
+        <v>0.453333</v>
       </c>
       <c r="B141" t="n">
-        <v>0.968966</v>
+        <v>0.87931</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0.728889</v>
+        <v>0.457778</v>
       </c>
       <c r="B142" t="n">
-        <v>0.972414</v>
+        <v>0.87931</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0.751111</v>
+        <v>0.457778</v>
       </c>
       <c r="B143" t="n">
-        <v>0.972414</v>
+        <v>0.882759</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0.751111</v>
+        <v>0.497778</v>
       </c>
       <c r="B144" t="n">
-        <v>0.975862</v>
+        <v>0.882759</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0.76</v>
+        <v>0.497778</v>
       </c>
       <c r="B145" t="n">
-        <v>0.975862</v>
+        <v>0.886207</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0.76</v>
+        <v>0.537778</v>
       </c>
       <c r="B146" t="n">
-        <v>0.97931</v>
+        <v>0.886207</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0.822222</v>
+        <v>0.537778</v>
       </c>
       <c r="B147" t="n">
-        <v>0.97931</v>
+        <v>0.889655</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>0.822222</v>
+        <v>0.5644439999999999</v>
       </c>
       <c r="B148" t="n">
-        <v>0.982759</v>
+        <v>0.889655</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0.831111</v>
+        <v>0.5644439999999999</v>
       </c>
       <c r="B149" t="n">
-        <v>0.982759</v>
+        <v>0.893103</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>0.831111</v>
+        <v>0.586667</v>
       </c>
       <c r="B150" t="n">
-        <v>0.9862069999999999</v>
+        <v>0.893103</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>0.848889</v>
+        <v>0.586667</v>
       </c>
       <c r="B151" t="n">
-        <v>0.9862069999999999</v>
+        <v>0.903448</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.848889</v>
+        <v>0.604444</v>
       </c>
       <c r="B152" t="n">
-        <v>0.989655</v>
+        <v>0.903448</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0.866667</v>
+        <v>0.604444</v>
       </c>
       <c r="B153" t="n">
-        <v>0.989655</v>
+        <v>0.906897</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0.866667</v>
+        <v>0.617778</v>
       </c>
       <c r="B154" t="n">
-        <v>0.993103</v>
+        <v>0.906897</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0.915556</v>
+        <v>0.617778</v>
       </c>
       <c r="B155" t="n">
-        <v>0.993103</v>
+        <v>0.913793</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0.915556</v>
+        <v>0.644444</v>
       </c>
       <c r="B156" t="n">
-        <v>0.996552</v>
+        <v>0.913793</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>0.942222</v>
+        <v>0.644444</v>
       </c>
       <c r="B157" t="n">
-        <v>0.996552</v>
+        <v>0.917241</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>0.942222</v>
+        <v>0.648889</v>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>0.917241</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
+        <v>0.648889</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0.92069</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>0.6844440000000001</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.92069</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>0.6844440000000001</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0.924138</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>0.711111</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.924138</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>0.711111</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.927586</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>0.715556</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0.927586</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>0.715556</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.931034</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>0.777778</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.931034</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>0.777778</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0.937931</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>0.782222</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.937931</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>0.782222</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.944828</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>0.786667</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.944828</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>0.786667</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.951724</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>0.813333</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0.951724</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>0.813333</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0.955172</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>0.826667</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0.955172</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>0.826667</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0.9586209999999999</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>0.844444</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0.9586209999999999</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>0.844444</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0.962069</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>0.866667</v>
+      </c>
+      <c r="B178" t="n">
+        <v>0.962069</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>0.866667</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0.965517</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>0.871111</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0.965517</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>0.871111</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0.972414</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="B182" t="n">
+        <v>0.972414</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0.975862</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0.975862</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0.982759</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>0.968889</v>
+      </c>
+      <c r="B186" t="n">
+        <v>0.982759</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>0.968889</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0.989655</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>0.973333</v>
+      </c>
+      <c r="B188" t="n">
+        <v>0.989655</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>0.973333</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0.993103</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>0.977778</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0.993103</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>0.977778</v>
+      </c>
+      <c r="B191" t="n">
+        <v>0.996552</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>0.982222</v>
+      </c>
+      <c r="B192" t="n">
+        <v>0.996552</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>0.982222</v>
+      </c>
+      <c r="B193" t="n">
         <v>1</v>
       </c>
-      <c r="B159" t="n">
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>1</v>
+      </c>
+      <c r="B194" t="n">
         <v>1</v>
       </c>
     </row>
